--- a/examples/wangetal2018/out/ResultFiles/AC_0.2_b.xlsx
+++ b/examples/wangetal2018/out/ResultFiles/AC_0.2_b.xlsx
@@ -14,17 +14,18 @@
     <sheet name="Compressor design" sheetId="5" r:id="rId5"/>
     <sheet name="Pressure profile" sheetId="6" r:id="rId6"/>
     <sheet name="Demand error" sheetId="7" r:id="rId7"/>
+    <sheet name="ProFAST" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="316">
   <si>
     <t xml:space="preserve">
 ---------DISCLAIMER---------
-AS NOTED IN THE LICENSE, ALLIANCE FOR SUSTAINABLE ENERGY, LLC: (i) DISCLAIMS ANY WARRANTIES, EXPRESS OR IMPLIED, INCLUDING BUT NOT LIMITED TO ANY IMPLIED WARRANTIES OF MERCHANTABILITY, FITNESS FOR A PARTICULAR PURPOSE, TITLE OR NON-INFRINGEMENT, AND (ii) DOES NOT ASSUME ANY LEGAL LIABILITY OR RESPONSIBILITY FOR THE ACCURACY, COMPLETENESS, OR USEFULNESS OF SOFTWARE OR ITS OUTPUTS. ANY RELIANCE BY THE USER ON THE SOFTWARE IS DONE AT THE USER’S OWN RISK.
+AS NOTED IN THE LICENSE, ALLIANCE FOR ENERGY INNOVATION, LLC: (i) DISCLAIMS ANY WARRANTIES, EXPRESS OR IMPLIED, INCLUDING BUT NOT LIMITED TO ANY IMPLIED WARRANTIES OF MERCHANTABILITY, FITNESS FOR A PARTICULAR PURPOSE, TITLE OR NON-INFRINGEMENT, AND (ii) DOES NOT ASSUME ANY LEGAL LIABILITY OR RESPONSIBILITY FOR THE ACCURACY, COMPLETENESS, OR USEFULNESS OF SOFTWARE OR ITS OUTPUTS. ANY RELIANCE BY THE USER ON THE SOFTWARE IS DONE AT THE USER’S OWN RISK.
 BlendPATH was developed to provide the user with economic analytical capabilities to evaluate potential natural gas transmission pipeline modifications for accommodating hydrogen blending or pure hydrogen streams and to assess the potential associated economic impacts. This model is intended for use during the early stages of pipeline repurposing concept evaluation, which is defined here as the initial project phase when the developer has already gathered the relevant pipeline material design and operation data but has not yet conducted the detailed pipeline materials testing, as specified in ASME B31.12, or performed the in-line inspections that qualify a given pipeline section for hydrogen or hydrogen blending service. Despite BlendPATH using ASME B31.12 to assess existing natural gas transmission pipelines and establish potential pipeline modifications for a natural gas transmission pipeline network to meet ASME B31.12 design requirements, BlendPATH does not qualify the examined pipeline network or modifications thereof for pure hydrogen or hydrogen blending. Pipeline owners and operators must conduct additional evaluations as specified in ASME B31.12 and other relevant code and regulations, independent of BlendPATH application, to qualify actual natural gas transmission pipelines for operation with hydrogen. Failure to do so may result in pipeline fatigue and/or rupture. It is the sole responsibility of the pipeline owner and operator to ensure that their pipeline qualifies for the ASME B31.12 design option that they choose, and any other relevant code and regulations, and that any defects present in the pipeline are acceptable at the operating pressure chosen.
 ----------------------------
 </t>
@@ -39,12 +40,21 @@
     <t>Network name</t>
   </si>
   <si>
+    <t>examples/wangetal2018</t>
+  </si>
+  <si>
     <t>Save directory</t>
   </si>
   <si>
+    <t>out</t>
+  </si>
+  <si>
     <t>Design option - original</t>
   </si>
   <si>
+    <t>b</t>
+  </si>
+  <si>
     <t>Location class</t>
   </si>
   <si>
@@ -57,6 +67,9 @@
     <t>Compression ratio</t>
   </si>
   <si>
+    <t>[1.2, 1.4, 1.6, 1.8, 2.0]</t>
+  </si>
+  <si>
     <t>Blending ratio</t>
   </si>
   <si>
@@ -75,18 +88,24 @@
     <t>Region</t>
   </si>
   <si>
+    <t>GP</t>
+  </si>
+  <si>
     <t>Modification method</t>
   </si>
   <si>
+    <t>ac</t>
+  </si>
+  <si>
     <t>Modification design option</t>
   </si>
   <si>
-    <t>Verbose</t>
-  </si>
-  <si>
     <t>Equation of state</t>
   </si>
   <si>
+    <t>rk</t>
+  </si>
+  <si>
     <t>Inline inspection inspection interval</t>
   </si>
   <si>
@@ -111,25 +130,40 @@
     <t>New electric compressor driver efficiency</t>
   </si>
   <si>
-    <t>examples/wangetal2018</t>
-  </si>
-  <si>
-    <t>out</t>
-  </si>
-  <si>
-    <t>b</t>
-  </si>
-  <si>
-    <t>[1.2, 1.4, 1.6, 1.8, 2.0]</t>
-  </si>
-  <si>
-    <t>GP</t>
-  </si>
-  <si>
-    <t>ac</t>
-  </si>
-  <si>
-    <t>rk</t>
+    <t>Pipe price markup</t>
+  </si>
+  <si>
+    <t>Compressor price markup</t>
+  </si>
+  <si>
+    <t>Financial overrides</t>
+  </si>
+  <si>
+    <t>{}</t>
+  </si>
+  <si>
+    <t>Filename suffix</t>
+  </si>
+  <si>
+    <t>Thermodynamic curvefits enabled</t>
+  </si>
+  <si>
+    <t>Composition tracking enabled</t>
+  </si>
+  <si>
+    <t>Scenario type</t>
+  </si>
+  <si>
+    <t>transmission</t>
+  </si>
+  <si>
+    <t>Polymer cost type</t>
+  </si>
+  <si>
+    <t>socal</t>
+  </si>
+  <si>
+    <t>Max velocity allowed in distribution networks</t>
   </si>
   <si>
     <t>Parameter</t>
@@ -141,6 +175,9 @@
     <t>LCOT: Levelized cost of transport</t>
   </si>
   <si>
+    <t>$/MMBTU</t>
+  </si>
+  <si>
     <t>LCOT: New pipe CapEx</t>
   </si>
   <si>
@@ -177,6 +214,12 @@
     <t>LCOT: Supply commpressor fuel</t>
   </si>
   <si>
+    <t>LCOT: Meter set assembly</t>
+  </si>
+  <si>
+    <t>LCOT: Gas pressure regulation and metering station</t>
+  </si>
+  <si>
     <t>LCOT: Fixed O&amp;M</t>
   </si>
   <si>
@@ -189,6 +232,9 @@
     <t>Hydrogen injection price</t>
   </si>
   <si>
+    <t>$/kg</t>
+  </si>
+  <si>
     <t>Natural gas price</t>
   </si>
   <si>
@@ -198,27 +244,48 @@
     <t>Pipeline capacity (daily)</t>
   </si>
   <si>
+    <t>MMBTU/day</t>
+  </si>
+  <si>
     <t>Pipeline capacity (hour)</t>
   </si>
   <si>
+    <t>MMBTU/hr</t>
+  </si>
+  <si>
     <t>Added pipeline</t>
   </si>
   <si>
+    <t>km</t>
+  </si>
+  <si>
+    <t>mi</t>
+  </si>
+  <si>
     <t>Added compressor stations</t>
   </si>
   <si>
     <t>Added compressor capacity</t>
   </si>
   <si>
+    <t>hp</t>
+  </si>
+  <si>
     <t>Compressor fuel usage</t>
   </si>
   <si>
     <t>Compressor fuel usage (electric)</t>
   </si>
   <si>
+    <t>kW</t>
+  </si>
+  <si>
     <t>New pipe</t>
   </si>
   <si>
+    <t>$</t>
+  </si>
+  <si>
     <t>New compressor stations</t>
   </si>
   <si>
@@ -231,39 +298,30 @@
     <t>Valve modifications</t>
   </si>
   <si>
+    <t>Meter set assembly</t>
+  </si>
+  <si>
+    <t>Gas pressure regulating metering station</t>
+  </si>
+  <si>
     <t>Hydrogen energy ratio</t>
   </si>
   <si>
-    <t>$/MMBTU</t>
-  </si>
-  <si>
-    <t>$/kg</t>
-  </si>
-  <si>
-    <t>MMBTU/day</t>
-  </si>
-  <si>
-    <t>MMBTU/hr</t>
-  </si>
-  <si>
-    <t>km</t>
-  </si>
-  <si>
-    <t>mi</t>
-  </si>
-  <si>
-    <t>hp</t>
-  </si>
-  <si>
-    <t>kW</t>
-  </si>
-  <si>
-    <t>$</t>
-  </si>
-  <si>
     <t>%</t>
   </si>
   <si>
+    <t>Emissions intensity (total)</t>
+  </si>
+  <si>
+    <t>kgCO2e/MMBTU</t>
+  </si>
+  <si>
+    <t>Total emissions (annual)</t>
+  </si>
+  <si>
+    <t>MMTCO2e/yr</t>
+  </si>
+  <si>
     <t>Breakdown of original pipe by diameter, schedule and grade</t>
   </si>
   <si>
@@ -279,6 +337,9 @@
     <t>Schedule</t>
   </si>
   <si>
+    <t>Polymer</t>
+  </si>
+  <si>
     <t>X60</t>
   </si>
   <si>
@@ -390,168 +451,168 @@
     <t>PI01_0</t>
   </si>
   <si>
+    <t>N01</t>
+  </si>
+  <si>
+    <t>N01_0</t>
+  </si>
+  <si>
+    <t>Existing</t>
+  </si>
+  <si>
     <t>PI01_1</t>
   </si>
   <si>
+    <t>N01_1</t>
+  </si>
+  <si>
     <t>PI01</t>
   </si>
   <si>
+    <t>N02</t>
+  </si>
+  <si>
     <t>PI02_0</t>
   </si>
   <si>
+    <t>N02_0</t>
+  </si>
+  <si>
     <t>PI02</t>
   </si>
   <si>
+    <t>N03</t>
+  </si>
+  <si>
     <t>PI03_0</t>
   </si>
   <si>
+    <t>N03_C</t>
+  </si>
+  <si>
+    <t>N03_C_0</t>
+  </si>
+  <si>
     <t>PI03</t>
   </si>
   <si>
+    <t>N04</t>
+  </si>
+  <si>
     <t>PI04_0</t>
   </si>
   <si>
+    <t>N04_0</t>
+  </si>
+  <si>
     <t>PI04_1</t>
   </si>
   <si>
+    <t>N04_1</t>
+  </si>
+  <si>
     <t>PI04</t>
   </si>
   <si>
+    <t>N05</t>
+  </si>
+  <si>
     <t>PI05_0</t>
   </si>
   <si>
+    <t>N05_0</t>
+  </si>
+  <si>
     <t>PI05_1</t>
   </si>
   <si>
+    <t>N05_1</t>
+  </si>
+  <si>
     <t>PI05</t>
   </si>
   <si>
+    <t>N06</t>
+  </si>
+  <si>
     <t>PI06_0</t>
   </si>
   <si>
+    <t>N06_C</t>
+  </si>
+  <si>
+    <t>N06_C_0</t>
+  </si>
+  <si>
     <t>PI06_1</t>
   </si>
   <si>
+    <t>N06_C_1</t>
+  </si>
+  <si>
     <t>PI06</t>
   </si>
   <si>
+    <t>N07</t>
+  </si>
+  <si>
     <t>PI07_0</t>
   </si>
   <si>
+    <t>N07_0</t>
+  </si>
+  <si>
     <t>PI07_1</t>
   </si>
   <si>
+    <t>N07_1</t>
+  </si>
+  <si>
     <t>PI07</t>
   </si>
   <si>
+    <t>N08</t>
+  </si>
+  <si>
     <t>PI08_0</t>
   </si>
   <si>
+    <t>N08_C</t>
+  </si>
+  <si>
+    <t>N08_C_0</t>
+  </si>
+  <si>
     <t>PI08_1</t>
   </si>
   <si>
+    <t>N08_C_1</t>
+  </si>
+  <si>
     <t>PI08</t>
   </si>
   <si>
+    <t>N09</t>
+  </si>
+  <si>
     <t>PI09_0</t>
   </si>
   <si>
+    <t>N09_0</t>
+  </si>
+  <si>
     <t>PI09_1</t>
   </si>
   <si>
+    <t>N09_1</t>
+  </si>
+  <si>
     <t>PI09</t>
   </si>
   <si>
-    <t>N01</t>
-  </si>
-  <si>
-    <t>N01_0</t>
-  </si>
-  <si>
-    <t>N01_1</t>
-  </si>
-  <si>
-    <t>N02</t>
-  </si>
-  <si>
-    <t>N02_0</t>
-  </si>
-  <si>
-    <t>N03_C</t>
-  </si>
-  <si>
-    <t>N03_C_0</t>
-  </si>
-  <si>
-    <t>N04</t>
-  </si>
-  <si>
-    <t>N04_0</t>
-  </si>
-  <si>
-    <t>N04_1</t>
-  </si>
-  <si>
-    <t>N05</t>
-  </si>
-  <si>
-    <t>N05_0</t>
-  </si>
-  <si>
-    <t>N05_1</t>
-  </si>
-  <si>
-    <t>N06_C</t>
-  </si>
-  <si>
-    <t>N06_C_0</t>
-  </si>
-  <si>
-    <t>N06_C_1</t>
-  </si>
-  <si>
-    <t>N07</t>
-  </si>
-  <si>
-    <t>N07_0</t>
-  </si>
-  <si>
-    <t>N07_1</t>
-  </si>
-  <si>
-    <t>N08_C</t>
-  </si>
-  <si>
-    <t>N08_C_0</t>
-  </si>
-  <si>
-    <t>N08_C_1</t>
-  </si>
-  <si>
-    <t>N09</t>
-  </si>
-  <si>
-    <t>N09_0</t>
-  </si>
-  <si>
-    <t>N09_1</t>
-  </si>
-  <si>
-    <t>N03</t>
-  </si>
-  <si>
-    <t>N06</t>
-  </si>
-  <si>
-    <t>N08</t>
-  </si>
-  <si>
     <t>N10</t>
   </si>
   <si>
-    <t>Existing</t>
-  </si>
-  <si>
     <t>Segment</t>
   </si>
   <si>
@@ -616,22 +677,313 @@
   </si>
   <si>
     <t>N13</t>
+  </si>
+  <si>
+    <t>capacity</t>
+  </si>
+  <si>
+    <t>527617.1846909181</t>
+  </si>
+  <si>
+    <t>long term utilization</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>demand rampup</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>analysis start year</t>
+  </si>
+  <si>
+    <t>2020</t>
+  </si>
+  <si>
+    <t>operating life</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>installation months</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>TOPC</t>
+  </si>
+  <si>
+    <t>unit price</t>
+  </si>
+  <si>
+    <t>0.0</t>
+  </si>
+  <si>
+    <t>decay</t>
+  </si>
+  <si>
+    <t>support utilization</t>
+  </si>
+  <si>
+    <t>sunset years</t>
+  </si>
+  <si>
+    <t>commodity</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>Natural Gas-H2 Blend</t>
+  </si>
+  <si>
+    <t>unit</t>
+  </si>
+  <si>
+    <t>MMBTU</t>
+  </si>
+  <si>
+    <t>initial price</t>
+  </si>
+  <si>
+    <t>0.25</t>
+  </si>
+  <si>
+    <t>escalation</t>
+  </si>
+  <si>
+    <t>0.025</t>
+  </si>
+  <si>
+    <t>annual operating incentive</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>taxable</t>
+  </si>
+  <si>
+    <t>True</t>
+  </si>
+  <si>
+    <t>incidental revenue</t>
+  </si>
+  <si>
+    <t>credit card fees</t>
+  </si>
+  <si>
+    <t>sales tax</t>
+  </si>
+  <si>
+    <t>road tax</t>
+  </si>
+  <si>
+    <t>labor</t>
+  </si>
+  <si>
+    <t>rate</t>
+  </si>
+  <si>
+    <t>maintenance</t>
+  </si>
+  <si>
+    <t>rent</t>
+  </si>
+  <si>
+    <t>license and permit</t>
+  </si>
+  <si>
+    <t>non depr assets</t>
+  </si>
+  <si>
+    <t>end of proj sale non depr assets</t>
+  </si>
+  <si>
+    <t>installation cost</t>
+  </si>
+  <si>
+    <t>depr type</t>
+  </si>
+  <si>
+    <t>Straight line</t>
+  </si>
+  <si>
+    <t>depr period</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>depreciable</t>
+  </si>
+  <si>
+    <t>one time cap inct</t>
+  </si>
+  <si>
+    <t>MACRS</t>
+  </si>
+  <si>
+    <t>property tax and insurance</t>
+  </si>
+  <si>
+    <t>0.009</t>
+  </si>
+  <si>
+    <t>admin expense</t>
+  </si>
+  <si>
+    <t>0.005</t>
+  </si>
+  <si>
+    <t>tax loss carry forward years</t>
+  </si>
+  <si>
+    <t>capital gains tax rate</t>
+  </si>
+  <si>
+    <t>0.15</t>
+  </si>
+  <si>
+    <t>tax losses monetized</t>
+  </si>
+  <si>
+    <t>sell undepreciated cap</t>
+  </si>
+  <si>
+    <t>loan period if used</t>
+  </si>
+  <si>
+    <t>debt equity ratio of initial financing</t>
+  </si>
+  <si>
+    <t>0.62</t>
+  </si>
+  <si>
+    <t>debt interest rate</t>
+  </si>
+  <si>
+    <t>0.07</t>
+  </si>
+  <si>
+    <t>debt type</t>
+  </si>
+  <si>
+    <t>Revolving debt</t>
+  </si>
+  <si>
+    <t>total income tax rate</t>
+  </si>
+  <si>
+    <t>0.2574</t>
+  </si>
+  <si>
+    <t>cash onhand</t>
+  </si>
+  <si>
+    <t>general inflation rate</t>
+  </si>
+  <si>
+    <t>leverage after tax nominal discount rate</t>
+  </si>
+  <si>
+    <t>0.13</t>
+  </si>
+  <si>
+    <t>fraction of year operated</t>
+  </si>
+  <si>
+    <t>[0. 0. 0. 0. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1.
+ 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1.
+ 1. 1. 1. 1. 1. 1.]</t>
+  </si>
+  <si>
+    <t>New pipe CapEx</t>
+  </si>
+  <si>
+    <t>cost</t>
+  </si>
+  <si>
+    <t>depr_type</t>
+  </si>
+  <si>
+    <t>depr_period</t>
+  </si>
+  <si>
+    <t>refurb</t>
+  </si>
+  <si>
+    <t>[0]</t>
+  </si>
+  <si>
+    <t>New compression capacity CapEx</t>
+  </si>
+  <si>
+    <t>Refurbished compressor capacity CapEx</t>
+  </si>
+  <si>
+    <t>50748077.07023712</t>
+  </si>
+  <si>
+    <t>Supply compressor CapEx</t>
+  </si>
+  <si>
+    <t>Meter &amp; regulator station modification CapEx</t>
+  </si>
+  <si>
+    <t>10486757.29473448</t>
+  </si>
+  <si>
+    <t>Valve replacement CapEx</t>
+  </si>
+  <si>
+    <t>24862120.0</t>
+  </si>
+  <si>
+    <t>Original network residual value</t>
+  </si>
+  <si>
+    <t>Gas pressure regulation and metering station</t>
+  </si>
+  <si>
+    <t>Compressor fuel</t>
+  </si>
+  <si>
+    <t>{'2048': np.float64(18.51020451680288), '2049': np.float64(18.972959629722947), '2050': np.float64(19.447283620466017), '2051': np.float64(19.933465710977668), '2052': np.float64(20.431802353752108), '2053': np.float64(20.94259741259591), '2054': np.float64(21.466162347910803), '2055': np.float64(22.002816406608567), '2056': np.float64(22.552886816773782), '2057': np.float64(23.116708987193125), '2058': np.float64(23.694626711872953), '2059': np.float64(24.286992379669773), '2060': np.float64(24.894167189161518), '2061': np.float64(25.516521368890555), '2062': np.float64(26.154434403112816), '2063': np.float64(26.808295263190633), '2064': np.float64(27.478502644770398), '2065': np.float64(28.165465210889653), '2066': np.float64(28.869601841161888), '2067': np.float64(29.591341887190936), '2068': np.float64(30.331125434370712), '2069': np.float64(31.089403570229972), '2070': np.float64(31.866638659485716), '2071': np.float64(32.663304625972856), '2072': np.float64(33.47988724162218), '2073': np.float64(34.31688442266273), '2074': np.float64(35.174806533229294), '2075': np.float64(36.05417669656002), '2076': np.float64(36.95553111397402), '2077': np.float64(37.87941939182336), '2078': np.float64(38.82640487661895), '2079': np.float64(39.79706499853442), '2080': np.float64(40.79199162349778), '2081': np.float64(41.81179141408522), '2082': np.float64(42.85708619943734), '2020': np.float64(9.271350212696891), '2021': np.float64(9.503133968014312), '2022': np.float64(9.740712317214669), '2023': np.float64(9.984230125145036), '2024': np.float64(10.23383587827366), '2025': np.float64(10.4896817752305), '2026': np.float64(10.75192381961126), '2027': np.float64(11.020721915101543), '2028': np.float64(11.29623996297908), '2029': np.float64(11.578645962053557), '2030': np.float64(11.868112111104894), '2031': np.float64(12.164814913882516), '2032': np.float64(12.468935286729579), '2033': np.float64(12.780658668897814), '2034': np.float64(13.100175135620262), '2035': np.float64(13.427679514010764), '2036': np.float64(13.763371501861034), '2037': np.float64(14.107455789407558), '2038': np.float64(14.460142184142745), '2039': np.float64(14.821645738746312), '2040': np.float64(15.192186882214969), '2041': np.float64(15.571991554270344), '2042': np.float64(15.9612913431271), '2043': np.float64(16.360323626705277), '2044': np.float64(16.769331717372904), '2045': np.float64(17.18856501030723), '2046': np.float64(17.618279135564904), '2047': np.float64(18.058736113954026)}</t>
+  </si>
+  <si>
+    <t>usage</t>
+  </si>
+  <si>
+    <t>0.004903209855497961</t>
+  </si>
+  <si>
+    <t>Compressor fuel (electric)</t>
+  </si>
+  <si>
+    <t>Supply commpressor fuel (electric)</t>
+  </si>
+  <si>
+    <t>Supply commpressor fuel</t>
+  </si>
+  <si>
+    <t>In-line inspection</t>
+  </si>
+  <si>
+    <t>3277333.333333336</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -647,7 +999,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -655,32 +1007,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -994,14 +1328,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1010,28 +1344,28 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -1039,7 +1373,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -1047,7 +1381,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -1055,15 +1389,15 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B9">
         <v>0.2</v>
@@ -1071,7 +1405,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B10">
         <v>7.39</v>
@@ -1079,7 +1413,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B11">
         <v>4.40756</v>
@@ -1087,7 +1421,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B12">
         <v>0.07000000000000001</v>
@@ -1095,7 +1429,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B13">
         <v>3.325</v>
@@ -1103,63 +1437,63 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" t="b">
-        <v>1</v>
+        <v>24</v>
+      </c>
+      <c r="B17" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" t="s">
-        <v>34</v>
+        <v>26</v>
+      </c>
+      <c r="B18">
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B19">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20">
+        <v>28</v>
+      </c>
+      <c r="B20" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B21" t="b">
         <v>0</v>
@@ -1167,39 +1501,100 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" t="b">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="B22">
+        <v>0.78</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="B23">
-        <v>0.78</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="B24">
-        <v>0.88</v>
+        <v>0.357</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>26</v>
-      </c>
-      <c r="B25">
-        <v>0.357</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>34</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>36</v>
+      </c>
+      <c r="B28" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1209,268 +1604,268 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>36</v>
+      <c r="C1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B2">
-        <v>0.1341347006259175</v>
+        <v>0.1326083249258077</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B5">
-        <v>0.031381991683298</v>
+        <v>0.03136208429853531</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="B6">
         <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="B7">
-        <v>0.006484882762210725</v>
+        <v>0.00648076903171232</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="B8">
-        <v>0.01537443166544618</v>
+        <v>0.01536467878775248</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
       <c r="C9" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="B10">
         <v>0.01701801172198348</v>
       </c>
       <c r="C10" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="B11">
-        <v>0.04692069938970514</v>
+        <v>0.04545937573666854</v>
       </c>
       <c r="C11" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
       <c r="C12" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B13">
         <v>0</v>
       </c>
       <c r="C13" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="B14">
         <v>0</v>
       </c>
       <c r="C14" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="B15">
-        <v>0.001953097288743741</v>
+        <v>0</v>
       </c>
       <c r="C15" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="B16">
-        <v>0.01447810371480994</v>
+        <v>0</v>
       </c>
       <c r="C16" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="B17">
-        <v>0.0005234823997202223</v>
+        <v>0.001945465410243192</v>
       </c>
       <c r="C17" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B18">
-        <v>4.40756</v>
+        <v>0.01446332376341934</v>
       </c>
       <c r="C18" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="B19">
-        <v>7.39</v>
+        <v>0.0005146161754929709</v>
       </c>
       <c r="C19" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="B20">
-        <v>9.271350212696891</v>
+        <v>4.40756</v>
       </c>
       <c r="C20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="B21">
-        <v>527617.1846909181</v>
+        <v>7.39</v>
       </c>
       <c r="C21" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="B22">
-        <v>21984.04936212159</v>
+        <v>9.271350212696891</v>
       </c>
       <c r="C22" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>527617.1846909181</v>
       </c>
       <c r="C23" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>21984.04936212159</v>
       </c>
       <c r="C24" t="s">
         <v>74</v>
@@ -1478,292 +1873,361 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="B25">
         <v>0</v>
       </c>
+      <c r="C25" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="B26">
         <v>0</v>
       </c>
       <c r="C26" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="B27">
-        <v>2670.179288645802</v>
-      </c>
-      <c r="C27" t="s">
-        <v>71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="B28">
-        <v>111.2574703602418</v>
+        <v>0</v>
       </c>
       <c r="C28" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>2587.017779906597</v>
       </c>
       <c r="C29" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>107.7924074961082</v>
       </c>
       <c r="C30" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="B31">
         <v>0</v>
       </c>
       <c r="C31" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="B32">
+        <v>0</v>
+      </c>
+      <c r="C32" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" t="s">
+        <v>86</v>
+      </c>
+      <c r="B33">
+        <v>0</v>
+      </c>
+      <c r="C33" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" t="s">
+        <v>87</v>
+      </c>
+      <c r="B34">
         <v>50748077.07023712</v>
       </c>
-      <c r="C32" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" t="s">
-        <v>66</v>
-      </c>
-      <c r="B33">
+      <c r="C34" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" t="s">
+        <v>88</v>
+      </c>
+      <c r="B35">
         <v>10486757.29473448</v>
       </c>
-      <c r="C33" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" t="s">
-        <v>67</v>
-      </c>
-      <c r="B34">
+      <c r="C35" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" t="s">
+        <v>89</v>
+      </c>
+      <c r="B36">
         <v>24862120</v>
       </c>
-      <c r="C34" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" t="s">
-        <v>68</v>
-      </c>
-      <c r="B35">
+      <c r="C36" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" t="s">
+        <v>90</v>
+      </c>
+      <c r="B37">
+        <v>0</v>
+      </c>
+      <c r="C37" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" t="s">
+        <v>91</v>
+      </c>
+      <c r="B38">
+        <v>0</v>
+      </c>
+      <c r="C38" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" t="s">
+        <v>92</v>
+      </c>
+      <c r="B39">
         <v>7.406825856025969</v>
       </c>
-      <c r="C35" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8">
-      <c r="A41">
+      <c r="C39" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" t="s">
+        <v>94</v>
+      </c>
+      <c r="B40">
+        <v>59.06801042118317</v>
+      </c>
+      <c r="C40" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" t="s">
+        <v>96</v>
+      </c>
+      <c r="B41">
+        <v>11.37533353775724</v>
+      </c>
+      <c r="C41" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" t="s">
+        <v>99</v>
+      </c>
+      <c r="B47" t="s">
+        <v>100</v>
+      </c>
+      <c r="C47" t="s">
+        <v>101</v>
+      </c>
+      <c r="D47" t="s">
+        <v>102</v>
+      </c>
+      <c r="E47" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48">
         <v>650</v>
       </c>
-      <c r="B41">
+      <c r="B48">
         <v>400.0000000000002</v>
       </c>
-      <c r="C41" t="s">
-        <v>84</v>
-      </c>
-      <c r="D41" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8">
-      <c r="A45" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8">
-      <c r="A46" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8">
-      <c r="A50" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8">
-      <c r="A51" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8">
-      <c r="A52" t="s">
-        <v>101</v>
-      </c>
-      <c r="B52">
-        <v>3.974822372013191</v>
-      </c>
-      <c r="C52">
-        <v>12.5</v>
-      </c>
-      <c r="D52">
-        <v>0</v>
-      </c>
-      <c r="E52">
-        <v>0</v>
-      </c>
-      <c r="F52">
-        <v>16916025.69007904</v>
-      </c>
-      <c r="G52">
-        <v>37.9904862347693</v>
-      </c>
-      <c r="H52">
-        <v>0</v>
+      <c r="C48" t="s">
+        <v>104</v>
+      </c>
+      <c r="D48" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" t="s">
-        <v>102</v>
-      </c>
-      <c r="B53">
-        <v>4.724218021884663</v>
-      </c>
-      <c r="C53">
-        <v>12.5</v>
-      </c>
-      <c r="D53">
-        <v>0</v>
-      </c>
-      <c r="E53">
-        <v>0</v>
-      </c>
-      <c r="F53">
-        <v>16916025.69007904</v>
-      </c>
-      <c r="G53">
-        <v>45.15304658496141</v>
-      </c>
-      <c r="H53">
-        <v>0</v>
+        <v>106</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B54">
-        <v>2.941470851697919</v>
-      </c>
-      <c r="C54">
+        <v>99</v>
+      </c>
+      <c r="B54" t="s">
+        <v>100</v>
+      </c>
+      <c r="C54" t="s">
+        <v>107</v>
+      </c>
+      <c r="D54" t="s">
+        <v>102</v>
+      </c>
+      <c r="E54" t="s">
+        <v>108</v>
+      </c>
+      <c r="F54" t="s">
+        <v>109</v>
+      </c>
+      <c r="G54" t="s">
+        <v>110</v>
+      </c>
+      <c r="H54" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" t="s">
+        <v>113</v>
+      </c>
+      <c r="B60" t="s">
+        <v>114</v>
+      </c>
+      <c r="C60" t="s">
+        <v>115</v>
+      </c>
+      <c r="D60" t="s">
+        <v>116</v>
+      </c>
+      <c r="E60" t="s">
+        <v>117</v>
+      </c>
+      <c r="F60" t="s">
+        <v>118</v>
+      </c>
+      <c r="G60" t="s">
+        <v>119</v>
+      </c>
+      <c r="H60" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" t="s">
+        <v>121</v>
+      </c>
+      <c r="B61">
+        <v>3.862295623552853</v>
+      </c>
+      <c r="C61">
         <v>12.5</v>
       </c>
-      <c r="D54">
+      <c r="D61">
         <v>0</v>
       </c>
-      <c r="E54">
+      <c r="E61">
         <v>0</v>
       </c>
-      <c r="F54">
+      <c r="F61">
         <v>16916025.69007904</v>
       </c>
-      <c r="G54">
-        <v>28.11393754051108</v>
-      </c>
-      <c r="H54">
+      <c r="G61">
+        <v>36.91498008925553</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" t="s">
+        <v>122</v>
+      </c>
+      <c r="B62">
+        <v>4.564730244937494</v>
+      </c>
+      <c r="C62">
+        <v>12.5</v>
+      </c>
+      <c r="D62">
+        <v>0</v>
+      </c>
+      <c r="E62">
+        <v>0</v>
+      </c>
+      <c r="F62">
+        <v>16916025.69007904</v>
+      </c>
+      <c r="G62">
+        <v>43.62869716059792</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" t="s">
+        <v>123</v>
+      </c>
+      <c r="B63">
+        <v>2.850946995583345</v>
+      </c>
+      <c r="C63">
+        <v>12.5</v>
+      </c>
+      <c r="D63">
+        <v>0</v>
+      </c>
+      <c r="E63">
+        <v>0</v>
+      </c>
+      <c r="F63">
+        <v>16916025.69007904</v>
+      </c>
+      <c r="G63">
+        <v>27.24873024625477</v>
+      </c>
+      <c r="H63">
         <v>0</v>
       </c>
     </row>
@@ -1778,59 +2242,59 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>119</v>
+      <c r="A1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G1" t="s">
+        <v>130</v>
+      </c>
+      <c r="H1" t="s">
+        <v>102</v>
+      </c>
+      <c r="I1" t="s">
+        <v>131</v>
+      </c>
+      <c r="J1" t="s">
+        <v>132</v>
+      </c>
+      <c r="K1" t="s">
+        <v>133</v>
+      </c>
+      <c r="L1" t="s">
+        <v>100</v>
+      </c>
+      <c r="M1" t="s">
+        <v>134</v>
+      </c>
+      <c r="N1" t="s">
+        <v>135</v>
+      </c>
+      <c r="O1" t="s">
+        <v>136</v>
+      </c>
+      <c r="P1" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>138</v>
+      </c>
+      <c r="R1" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -1838,31 +2302,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="C2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E2" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="F2">
-        <v>111.3599894075518</v>
+        <v>111.3428529272735</v>
       </c>
       <c r="G2">
         <v>650</v>
       </c>
       <c r="H2" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I2">
         <v>9.525</v>
       </c>
       <c r="J2" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K2">
         <v>8.758481331682836</v>
@@ -1877,16 +2341,16 @@
         <v>8700000</v>
       </c>
       <c r="O2">
-        <v>8476754.202064242</v>
+        <v>8479590.132587632</v>
       </c>
       <c r="P2">
-        <v>6.632446768962786</v>
+        <v>6.707768281131918</v>
       </c>
       <c r="Q2">
-        <v>0.01315926577815749</v>
+        <v>0.0133918587030595</v>
       </c>
       <c r="R2">
-        <v>17.12804673535513</v>
+        <v>17.01859662886778</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1894,31 +2358,31 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="C3" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E3" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="F3">
-        <v>111.3599846292779</v>
+        <v>111.3428524186157</v>
       </c>
       <c r="G3">
         <v>650</v>
       </c>
       <c r="H3" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I3">
         <v>9.525</v>
       </c>
       <c r="J3" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K3">
         <v>8.758481331682836</v>
@@ -1930,19 +2394,19 @@
         <v>8.284946666666665</v>
       </c>
       <c r="N3">
-        <v>8476754.202064242</v>
+        <v>8479590.132587632</v>
       </c>
       <c r="O3">
-        <v>8247156.249845068</v>
+        <v>8253070.573919045</v>
       </c>
       <c r="P3">
-        <v>6.637568057563104</v>
+        <v>6.898935744275372</v>
       </c>
       <c r="Q3">
-        <v>0.01318225271589652</v>
+        <v>0.01378909046527334</v>
       </c>
       <c r="R3">
-        <v>17.37692399388337</v>
+        <v>17.25940302416395</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1950,31 +2414,31 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>122</v>
+        <v>146</v>
       </c>
       <c r="C4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D4" t="s">
         <v>147</v>
       </c>
-      <c r="D4" t="s">
-        <v>148</v>
-      </c>
       <c r="E4" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="F4">
-        <v>111.3599793252426</v>
+        <v>111.3428518781118</v>
       </c>
       <c r="G4">
         <v>650</v>
       </c>
       <c r="H4" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I4">
         <v>9.525</v>
       </c>
       <c r="J4" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K4">
         <v>8.758481331682836</v>
@@ -1986,19 +2450,19 @@
         <v>8.284946666666665</v>
       </c>
       <c r="N4">
-        <v>8247156.249845068</v>
+        <v>8253070.573919045</v>
       </c>
       <c r="O4">
-        <v>8010637.823423402</v>
+        <v>8019907.674655082</v>
       </c>
       <c r="P4">
-        <v>6.642699030617529</v>
+        <v>7.107149930656364</v>
       </c>
       <c r="Q4">
-        <v>0.01320574085268655</v>
+        <v>0.0142220994606375</v>
       </c>
       <c r="R4">
-        <v>17.64458139811767</v>
+        <v>17.51791681657405</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -2006,31 +2470,31 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="C5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D5" t="s">
         <v>149</v>
       </c>
       <c r="E5" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="F5">
-        <v>111.3599720671571</v>
+        <v>111.3428511975295</v>
       </c>
       <c r="G5">
         <v>650</v>
       </c>
       <c r="H5" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I5">
         <v>9.525</v>
       </c>
       <c r="J5" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K5">
         <v>8.758481331682836</v>
@@ -2042,19 +2506,19 @@
         <v>9.320565</v>
       </c>
       <c r="N5">
-        <v>8010637.823423402</v>
+        <v>8019907.674655082</v>
       </c>
       <c r="O5">
-        <v>7735455.61826623</v>
+        <v>7748888.164341453</v>
       </c>
       <c r="P5">
-        <v>6.648485190587453</v>
+        <v>7.365294141460298</v>
       </c>
       <c r="Q5">
-        <v>0.0132326015690482</v>
+        <v>0.01475895440012647</v>
       </c>
       <c r="R5">
-        <v>17.97180028273407</v>
+        <v>17.83322012087873</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -2062,31 +2526,31 @@
         <v>0</v>
       </c>
       <c r="B6" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="C6" t="s">
         <v>149</v>
       </c>
       <c r="D6" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="E6" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="F6">
-        <v>111.3599642877714</v>
+        <v>111.3428505408204</v>
       </c>
       <c r="G6">
         <v>650</v>
       </c>
       <c r="H6" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I6">
         <v>9.525</v>
       </c>
       <c r="J6" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K6">
         <v>8.758481331682836</v>
@@ -2098,19 +2562,19 @@
         <v>9.320565</v>
       </c>
       <c r="N6">
-        <v>7735455.61826623</v>
+        <v>7748888.164341453</v>
       </c>
       <c r="O6">
-        <v>7449576.148832415</v>
+        <v>7467656.390149716</v>
       </c>
       <c r="P6">
-        <v>6.654286192144542</v>
+        <v>7.653377534840487</v>
       </c>
       <c r="Q6">
-        <v>0.01325992549378846</v>
+        <v>0.01535818294837508</v>
       </c>
       <c r="R6">
-        <v>18.33133246027575</v>
+        <v>18.17863594641723</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -2118,31 +2582,31 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="C7" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D7" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E7" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="F7">
-        <v>111.1689025334362</v>
+        <v>111.1568649536646</v>
       </c>
       <c r="G7">
         <v>650</v>
       </c>
       <c r="H7" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I7">
         <v>9.525</v>
       </c>
       <c r="J7" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K7">
         <v>8.758481331682836</v>
@@ -2157,16 +2621,16 @@
         <v>8758481.331682835</v>
       </c>
       <c r="O7">
-        <v>8496918.850601459</v>
+        <v>8500209.805146635</v>
       </c>
       <c r="P7">
-        <v>6.578431200458652</v>
+        <v>6.679714890591616</v>
       </c>
       <c r="Q7">
-        <v>0.01305097183140109</v>
+        <v>0.01333446453556326</v>
       </c>
       <c r="R7">
-        <v>17.10669354535391</v>
+        <v>16.99717358808287</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -2174,31 +2638,31 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>126</v>
+        <v>155</v>
       </c>
       <c r="C8" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D8" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E8" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="F8">
-        <v>111.1689023532048</v>
+        <v>111.1568649282199</v>
       </c>
       <c r="G8">
         <v>650</v>
       </c>
       <c r="H8" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I8">
         <v>9.525</v>
       </c>
       <c r="J8" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K8">
         <v>8.758481331682836</v>
@@ -2210,19 +2674,19 @@
         <v>9.786593249999999</v>
       </c>
       <c r="N8">
-        <v>8496918.850601459</v>
+        <v>8500209.805146635</v>
       </c>
       <c r="O8">
-        <v>8226615.089618172</v>
+        <v>8233529.345266046</v>
       </c>
       <c r="P8">
-        <v>6.584362319339492</v>
+        <v>6.904373068834018</v>
       </c>
       <c r="Q8">
-        <v>0.01307774007073833</v>
+        <v>0.0138013208587517</v>
       </c>
       <c r="R8">
-        <v>17.39968791073662</v>
+        <v>17.28064194879695</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -2230,31 +2694,31 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="C9" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D9" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="E9" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="F9">
-        <v>91.38325234028208</v>
+        <v>91.3712141999177</v>
       </c>
       <c r="G9">
         <v>650</v>
       </c>
       <c r="H9" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I9">
         <v>9.525</v>
       </c>
       <c r="J9" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K9">
         <v>8.758481331682836</v>
@@ -2266,19 +2730,19 @@
         <v>10.04549783333334</v>
       </c>
       <c r="N9">
-        <v>8226615.089618172</v>
+        <v>8233529.345266046</v>
       </c>
       <c r="O9">
-        <v>8032054.409684942</v>
+        <v>8041736.906089736</v>
       </c>
       <c r="P9">
-        <v>5.417506804056713</v>
+        <v>5.815903460180489</v>
       </c>
       <c r="Q9">
-        <v>0.01076907526074553</v>
+        <v>0.01163690907343733</v>
       </c>
       <c r="R9">
-        <v>17.61983451595798</v>
+        <v>17.49322120757788</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -2286,31 +2750,31 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>128</v>
+        <v>159</v>
       </c>
       <c r="C10" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D10" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="E10" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="F10">
-        <v>91.38325219593001</v>
+        <v>91.37121416636526</v>
       </c>
       <c r="G10">
         <v>650</v>
       </c>
       <c r="H10" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I10">
         <v>9.525</v>
       </c>
       <c r="J10" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K10">
         <v>8.758481331682836</v>
@@ -2322,19 +2786,19 @@
         <v>10.04549783333334</v>
       </c>
       <c r="N10">
-        <v>8032054.409684942</v>
+        <v>8041736.906089736</v>
       </c>
       <c r="O10">
-        <v>7832408.175842476</v>
+        <v>7845074.721111168</v>
       </c>
       <c r="P10">
-        <v>5.422538579477385</v>
+        <v>5.967326677160114</v>
       </c>
       <c r="Q10">
-        <v>0.01078811851904729</v>
+        <v>0.01195171402753788</v>
       </c>
       <c r="R10">
-        <v>17.85458970575013</v>
+        <v>17.71948520523761</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -2342,31 +2806,31 @@
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>129</v>
+        <v>161</v>
       </c>
       <c r="C11" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="D11" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="E11" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="F11">
-        <v>91.38325205585363</v>
+        <v>91.37121411957217</v>
       </c>
       <c r="G11">
         <v>650</v>
       </c>
       <c r="H11" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I11">
         <v>9.525</v>
       </c>
       <c r="J11" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K11">
         <v>8.758481331682836</v>
@@ -2378,19 +2842,19 @@
         <v>10.04549783333334</v>
       </c>
       <c r="N11">
-        <v>7832408.175842476</v>
+        <v>7845074.721111168</v>
       </c>
       <c r="O11">
-        <v>7627263.289575088</v>
+        <v>7643158.537122125</v>
       </c>
       <c r="P11">
-        <v>5.427584179334699</v>
+        <v>6.130967896958886</v>
       </c>
       <c r="Q11">
-        <v>0.01080754486523038</v>
+        <v>0.01229217033712129</v>
       </c>
       <c r="R11">
-        <v>18.1053642896564</v>
+        <v>17.96080156609528</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -2398,31 +2862,31 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>130</v>
+        <v>163</v>
       </c>
       <c r="C12" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="D12" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="E12" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="F12">
-        <v>91.38325185794812</v>
+        <v>91.37121403603372</v>
       </c>
       <c r="G12">
         <v>650</v>
       </c>
       <c r="H12" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I12">
         <v>9.525</v>
       </c>
       <c r="J12" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K12">
         <v>8.758481331682836</v>
@@ -2434,19 +2898,19 @@
         <v>10.35618333333334</v>
       </c>
       <c r="N12">
-        <v>7627263.289575088</v>
+        <v>7643158.537122125</v>
       </c>
       <c r="O12">
-        <v>7409513.485826758</v>
+        <v>7429029.878354515</v>
       </c>
       <c r="P12">
-        <v>5.432800357350804</v>
+        <v>6.314443312742941</v>
       </c>
       <c r="Q12">
-        <v>0.01082773106887062</v>
+        <v>0.01267386754349263</v>
       </c>
       <c r="R12">
-        <v>18.38332157952462</v>
+        <v>18.22756804973411</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2454,31 +2918,31 @@
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>131</v>
+        <v>165</v>
       </c>
       <c r="C13" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="D13" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="E13" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="F13">
-        <v>91.38325167738188</v>
+        <v>91.37121395742022</v>
       </c>
       <c r="G13">
         <v>650</v>
       </c>
       <c r="H13" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I13">
         <v>9.525</v>
       </c>
       <c r="J13" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K13">
         <v>8.758481331682836</v>
@@ -2490,19 +2954,19 @@
         <v>10.35618333333334</v>
       </c>
       <c r="N13">
-        <v>7409513.485826758</v>
+        <v>7429029.878354515</v>
       </c>
       <c r="O13">
-        <v>7184817.987150718</v>
+        <v>7208300.25772877</v>
       </c>
       <c r="P13">
-        <v>5.438031366813878</v>
+        <v>6.515142556012322</v>
       </c>
       <c r="Q13">
-        <v>0.01084835266780107</v>
+        <v>0.01309152522907533</v>
       </c>
       <c r="R13">
-        <v>18.68330956218793</v>
+        <v>18.51497608799306</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2510,31 +2974,31 @@
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>132</v>
+        <v>167</v>
       </c>
       <c r="C14" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="D14" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E14" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="F14">
-        <v>91.38325142644442</v>
+        <v>91.37121400021488</v>
       </c>
       <c r="G14">
         <v>650</v>
       </c>
       <c r="H14" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I14">
         <v>9.525</v>
       </c>
       <c r="J14" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K14">
         <v>8.758481331682836</v>
@@ -2546,19 +3010,19 @@
         <v>10.35618333333334</v>
       </c>
       <c r="N14">
-        <v>7184817.987150718</v>
+        <v>7208300.25772877</v>
       </c>
       <c r="O14">
-        <v>6952473.518239986</v>
+        <v>6980325.270833372</v>
       </c>
       <c r="P14">
-        <v>5.44327726313794</v>
+        <v>6.735836292347922</v>
       </c>
       <c r="Q14">
-        <v>0.01086921559208737</v>
+        <v>0.01355102622283198</v>
       </c>
       <c r="R14">
-        <v>19.00907814126651</v>
+        <v>18.82595237723801</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2566,31 +3030,31 @@
         <v>2</v>
       </c>
       <c r="B15" t="s">
-        <v>133</v>
+        <v>169</v>
       </c>
       <c r="C15" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="D15" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="E15" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="F15">
-        <v>91.1556875301509</v>
+        <v>91.15132692787711</v>
       </c>
       <c r="G15">
         <v>650</v>
       </c>
       <c r="H15" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I15">
         <v>9.525</v>
       </c>
       <c r="J15" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K15">
         <v>8.758481331682836</v>
@@ -2605,16 +3069,16 @@
         <v>8758481.331682835</v>
       </c>
       <c r="O15">
-        <v>8571822.2119294</v>
+        <v>8574128.593491327</v>
       </c>
       <c r="P15">
-        <v>5.395278995413867</v>
+        <v>5.428564866921441</v>
       </c>
       <c r="Q15">
-        <v>0.01070028209757008</v>
+        <v>0.0108327866502424</v>
       </c>
       <c r="R15">
-        <v>17.02806890232468</v>
+        <v>16.92103445477113</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2622,31 +3086,31 @@
         <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="C16" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="D16" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="E16" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="F16">
-        <v>91.15568752692037</v>
+        <v>91.15132692697033</v>
       </c>
       <c r="G16">
         <v>650</v>
       </c>
       <c r="H16" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I16">
         <v>9.525</v>
       </c>
       <c r="J16" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K16">
         <v>8.758481331682836</v>
@@ -2658,19 +3122,19 @@
         <v>10.35618333333334</v>
       </c>
       <c r="N16">
-        <v>8571822.2119294</v>
+        <v>8574128.593491327</v>
       </c>
       <c r="O16">
-        <v>8380796.176403366</v>
+        <v>8385570.050553365</v>
       </c>
       <c r="P16">
-        <v>5.400429033278283</v>
+        <v>5.555237086824088</v>
       </c>
       <c r="Q16">
-        <v>0.0107192237113918</v>
+        <v>0.01109609802601299</v>
       </c>
       <c r="R16">
-        <v>17.23076777015289</v>
+        <v>17.11731698675986</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2678,31 +3142,31 @@
         <v>2</v>
       </c>
       <c r="B17" t="s">
-        <v>135</v>
+        <v>174</v>
       </c>
       <c r="C17" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="D17" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="E17" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="F17">
-        <v>91.15568752464148</v>
+        <v>91.15132692514187</v>
       </c>
       <c r="G17">
         <v>650</v>
       </c>
       <c r="H17" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I17">
         <v>9.525</v>
       </c>
       <c r="J17" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K17">
         <v>8.758481331682836</v>
@@ -2714,19 +3178,19 @@
         <v>10.35618333333334</v>
       </c>
       <c r="N17">
-        <v>8380796.176403366</v>
+        <v>8385570.050553365</v>
       </c>
       <c r="O17">
-        <v>8185081.59519545</v>
+        <v>8192505.249674703</v>
       </c>
       <c r="P17">
-        <v>5.4055936132249</v>
+        <v>5.691159928260147</v>
       </c>
       <c r="Q17">
-        <v>0.01073840307870775</v>
+        <v>0.01137859182399239</v>
       </c>
       <c r="R17">
-        <v>17.4459903950581</v>
+        <v>17.32546058878724</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -2734,31 +3198,31 @@
         <v>2</v>
       </c>
       <c r="B18" t="s">
-        <v>136</v>
+        <v>176</v>
       </c>
       <c r="C18" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="D18" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="E18" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="F18">
-        <v>91.15568752221219</v>
+        <v>91.15132691902792</v>
       </c>
       <c r="G18">
         <v>650</v>
       </c>
       <c r="H18" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I18">
         <v>9.525</v>
       </c>
       <c r="J18" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K18">
         <v>8.758481331682836</v>
@@ -2770,19 +3234,19 @@
         <v>10.35618333333334</v>
       </c>
       <c r="N18">
-        <v>8185081.59519545</v>
+        <v>8192505.249674703</v>
       </c>
       <c r="O18">
-        <v>7984323.078793087</v>
+        <v>7994600.118958353</v>
       </c>
       <c r="P18">
-        <v>5.410772803135615</v>
+        <v>5.83742166396399</v>
       </c>
       <c r="Q18">
-        <v>0.01075785303336826</v>
+        <v>0.01168273613560059</v>
       </c>
       <c r="R18">
-        <v>17.67513135382083</v>
+        <v>17.54667882217257</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2790,31 +3254,31 @@
         <v>2</v>
       </c>
       <c r="B19" t="s">
-        <v>137</v>
+        <v>178</v>
       </c>
       <c r="C19" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="D19" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="E19" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="F19">
-        <v>91.15568751912319</v>
+        <v>91.15132692610065</v>
       </c>
       <c r="G19">
         <v>650</v>
       </c>
       <c r="H19" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I19">
         <v>9.525</v>
       </c>
       <c r="J19" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K19">
         <v>8.758481331682836</v>
@@ -2826,19 +3290,19 @@
         <v>10.35618333333334</v>
       </c>
       <c r="N19">
-        <v>7984323.078793087</v>
+        <v>7994600.118958353</v>
       </c>
       <c r="O19">
-        <v>7778110.194919406</v>
+        <v>7791472.955083853</v>
       </c>
       <c r="P19">
-        <v>5.415966671485901</v>
+        <v>5.995446999175796</v>
       </c>
       <c r="Q19">
-        <v>0.01077754354999096</v>
+        <v>0.01201135708514477</v>
       </c>
       <c r="R19">
-        <v>17.91994949000694</v>
+        <v>17.78259665807912</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2846,31 +3310,31 @@
         <v>2</v>
       </c>
       <c r="B20" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="C20" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="D20" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="E20" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="F20">
-        <v>91.15568751788678</v>
+        <v>91.15132693258619</v>
       </c>
       <c r="G20">
         <v>650</v>
       </c>
       <c r="H20" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I20">
         <v>9.525</v>
       </c>
       <c r="J20" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K20">
         <v>8.758481331682836</v>
@@ -2882,19 +3346,19 @@
         <v>10.35618333333334</v>
       </c>
       <c r="N20">
-        <v>7778110.194919406</v>
+        <v>7791472.955083853</v>
       </c>
       <c r="O20">
-        <v>7565984.567129556</v>
+        <v>7582697.115993719</v>
       </c>
       <c r="P20">
-        <v>5.421175287835569</v>
+        <v>6.166852396056035</v>
       </c>
       <c r="Q20">
-        <v>0.01079754109155305</v>
+        <v>0.01236789308793454</v>
       </c>
       <c r="R20">
-        <v>18.18234682377292</v>
+        <v>18.03500100211568</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2902,31 +3366,31 @@
         <v>3</v>
       </c>
       <c r="B21" t="s">
-        <v>139</v>
+        <v>182</v>
       </c>
       <c r="C21" t="s">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="D21" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="E21" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="F21">
-        <v>91.01399329870084</v>
+        <v>91.01399329885099</v>
       </c>
       <c r="G21">
         <v>650</v>
       </c>
       <c r="H21" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I21">
         <v>9.525</v>
       </c>
       <c r="J21" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K21">
         <v>8.758481331682836</v>
@@ -2941,16 +3405,16 @@
         <v>8758481.331682835</v>
       </c>
       <c r="O21">
-        <v>8572396.711523501</v>
+        <v>8574678.426173495</v>
       </c>
       <c r="P21">
-        <v>5.386892474027773</v>
+        <v>5.420025507812136</v>
       </c>
       <c r="Q21">
-        <v>0.01068362306355111</v>
+        <v>0.01081571603205601</v>
       </c>
       <c r="R21">
-        <v>17.02747004366793</v>
+        <v>16.92047193424058</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2958,31 +3422,31 @@
         <v>3</v>
       </c>
       <c r="B22" t="s">
-        <v>140</v>
+        <v>185</v>
       </c>
       <c r="C22" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="D22" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="E22" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="F22">
-        <v>91.0139932984452</v>
+        <v>91.01399329815631</v>
       </c>
       <c r="G22">
         <v>650</v>
       </c>
       <c r="H22" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I22">
         <v>9.525</v>
       </c>
       <c r="J22" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K22">
         <v>8.758481331682836</v>
@@ -2994,19 +3458,19 @@
         <v>10.35618333333334</v>
       </c>
       <c r="N22">
-        <v>8572396.711523501</v>
+        <v>8574678.426173495</v>
       </c>
       <c r="O22">
-        <v>8381972.647276633</v>
+        <v>8386695.332215465</v>
       </c>
       <c r="P22">
-        <v>5.392034507191156</v>
+        <v>5.546094937002953</v>
       </c>
       <c r="Q22">
-        <v>0.01070250818670585</v>
+        <v>0.01107777508980109</v>
       </c>
       <c r="R22">
-        <v>17.22949717162503</v>
+        <v>17.11612527364128</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -3014,31 +3478,31 @@
         <v>3</v>
       </c>
       <c r="B23" t="s">
-        <v>141</v>
+        <v>187</v>
       </c>
       <c r="C23" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="D23" t="s">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="E23" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="F23">
-        <v>91.01399329839475</v>
+        <v>91.01399329927231</v>
       </c>
       <c r="G23">
         <v>650</v>
       </c>
       <c r="H23" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I23">
         <v>9.525</v>
       </c>
       <c r="J23" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K23">
         <v>8.758481331682836</v>
@@ -3050,19 +3514,19 @@
         <v>10.35618333333334</v>
       </c>
       <c r="N23">
-        <v>8381972.647276633</v>
+        <v>8386695.332215465</v>
       </c>
       <c r="O23">
-        <v>8186890.613454849</v>
+        <v>8194234.416009014</v>
       </c>
       <c r="P23">
-        <v>5.397191059662685</v>
+        <v>5.681341541671709</v>
       </c>
       <c r="Q23">
-        <v>0.01072162808649034</v>
+        <v>0.01135886097697837</v>
       </c>
       <c r="R23">
-        <v>17.44396595551323</v>
+        <v>17.32356443800505</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -3070,31 +3534,31 @@
         <v>3</v>
       </c>
       <c r="B24" t="s">
-        <v>142</v>
+        <v>189</v>
       </c>
       <c r="C24" t="s">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="D24" t="s">
-        <v>168</v>
+        <v>190</v>
       </c>
       <c r="E24" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="F24">
-        <v>91.01399329833932</v>
+        <v>91.01399329941023</v>
       </c>
       <c r="G24">
         <v>650</v>
       </c>
       <c r="H24" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I24">
         <v>9.525</v>
       </c>
       <c r="J24" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K24">
         <v>8.758481331682836</v>
@@ -3106,19 +3570,19 @@
         <v>10.35618333333334</v>
       </c>
       <c r="N24">
-        <v>8186890.613454849</v>
+        <v>8194234.416009014</v>
       </c>
       <c r="O24">
-        <v>7986798.75156553</v>
+        <v>7996964.814865724</v>
       </c>
       <c r="P24">
-        <v>5.40236219941864</v>
+        <v>5.826837390910497</v>
       </c>
       <c r="Q24">
-        <v>0.0107410190106629</v>
+        <v>0.01166141476969993</v>
       </c>
       <c r="R24">
-        <v>17.67225047112911</v>
+        <v>17.54398534621112</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -3126,31 +3590,31 @@
         <v>3</v>
       </c>
       <c r="B25" t="s">
+        <v>191</v>
+      </c>
+      <c r="C25" t="s">
+        <v>190</v>
+      </c>
+      <c r="D25" t="s">
+        <v>192</v>
+      </c>
+      <c r="E25" t="s">
         <v>143</v>
       </c>
-      <c r="C25" t="s">
-        <v>168</v>
-      </c>
-      <c r="D25" t="s">
-        <v>169</v>
-      </c>
-      <c r="E25" t="s">
-        <v>174</v>
-      </c>
       <c r="F25">
-        <v>91.01399329827109</v>
+        <v>91.01399329897345</v>
       </c>
       <c r="G25">
         <v>650</v>
       </c>
       <c r="H25" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I25">
         <v>9.525</v>
       </c>
       <c r="J25" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K25">
         <v>8.758481331682836</v>
@@ -3162,19 +3626,19 @@
         <v>10.35618333333334</v>
       </c>
       <c r="N25">
-        <v>7986798.75156553</v>
+        <v>7996964.814865724</v>
       </c>
       <c r="O25">
-        <v>7781291.00300254</v>
+        <v>7794508.752074498</v>
       </c>
       <c r="P25">
-        <v>5.40754799492557</v>
+        <v>5.983995435222005</v>
       </c>
       <c r="Q25">
-        <v>0.01076064491032702</v>
+        <v>0.0119882275274533</v>
       </c>
       <c r="R25">
-        <v>17.91610086538234</v>
+        <v>17.77900423904423</v>
       </c>
     </row>
     <row r="26" spans="1:18">
@@ -3182,31 +3646,31 @@
         <v>3</v>
       </c>
       <c r="B26" t="s">
-        <v>144</v>
+        <v>193</v>
       </c>
       <c r="C26" t="s">
-        <v>169</v>
+        <v>192</v>
       </c>
       <c r="D26" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="E26" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="F26">
-        <v>91.01399329819894</v>
+        <v>91.01399329886847</v>
       </c>
       <c r="G26">
         <v>650</v>
       </c>
       <c r="H26" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I26">
         <v>9.525</v>
       </c>
       <c r="J26" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="K26">
         <v>8.758481331682836</v>
@@ -3218,19 +3682,19 @@
         <v>10.35618333333334</v>
       </c>
       <c r="N26">
-        <v>7781291.00300254</v>
+        <v>7794508.752074498</v>
       </c>
       <c r="O26">
-        <v>7569913.88275066</v>
+        <v>7586443.998568771</v>
       </c>
       <c r="P26">
-        <v>5.412748515102528</v>
+        <v>6.154403317838248</v>
       </c>
       <c r="Q26">
-        <v>0.01078058128432241</v>
+        <v>0.01234269303515433</v>
       </c>
       <c r="R26">
-        <v>18.1773810554387</v>
+        <v>18.0303760008239</v>
       </c>
     </row>
   </sheetData>
@@ -3244,73 +3708,73 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>186</v>
+      <c r="C1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F1" t="s">
+        <v>196</v>
+      </c>
+      <c r="G1" t="s">
+        <v>197</v>
+      </c>
+      <c r="H1" t="s">
+        <v>198</v>
+      </c>
+      <c r="I1" t="s">
+        <v>199</v>
+      </c>
+      <c r="J1" t="s">
+        <v>114</v>
+      </c>
+      <c r="K1" t="s">
+        <v>200</v>
+      </c>
+      <c r="L1" t="s">
+        <v>120</v>
+      </c>
+      <c r="M1" t="s">
+        <v>201</v>
+      </c>
+      <c r="N1" t="s">
+        <v>202</v>
+      </c>
+      <c r="O1" t="s">
+        <v>203</v>
+      </c>
+      <c r="P1" t="s">
+        <v>204</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>205</v>
+      </c>
+      <c r="R1" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="2" spans="1:18">
       <c r="B2" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="C2" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="D2" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E2" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="F2">
         <v>70</v>
@@ -3319,16 +3783,16 @@
         <v>43.49597</v>
       </c>
       <c r="H2">
-        <v>1.175701967024737</v>
+        <v>1.172855428007613</v>
       </c>
       <c r="I2">
-        <v>37.9904862347693</v>
+        <v>36.91498008925553</v>
       </c>
       <c r="J2">
-        <v>3.974822372013191</v>
+        <v>3.862295623552853</v>
       </c>
       <c r="K2">
-        <v>5330.316297317128</v>
+        <v>5179.415677096847</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -3354,16 +3818,16 @@
     </row>
     <row r="3" spans="1:18">
       <c r="B3" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="C3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D3" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="E3" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="F3">
         <v>200</v>
@@ -3372,16 +3836,16 @@
         <v>124.2742</v>
       </c>
       <c r="H3">
-        <v>1.259764788561185</v>
+        <v>1.25473828107686</v>
       </c>
       <c r="I3">
-        <v>45.15304658496141</v>
+        <v>43.62869716059792</v>
       </c>
       <c r="J3">
-        <v>4.724218021884663</v>
+        <v>4.564730244937494</v>
       </c>
       <c r="K3">
-        <v>6335.270851707772</v>
+        <v>6121.394553066079</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -3407,34 +3871,34 @@
     </row>
     <row r="4" spans="1:18">
       <c r="B4" t="s">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="C4" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="D4" t="s">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="E4" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="F4">
-        <v>300.0000000000001</v>
+        <v>300</v>
       </c>
       <c r="G4">
         <v>186.4113</v>
       </c>
       <c r="H4">
-        <v>1.157612899414847</v>
+        <v>1.155061477163463</v>
       </c>
       <c r="I4">
-        <v>28.11393754051108</v>
+        <v>27.24873024625477</v>
       </c>
       <c r="J4">
-        <v>2.941470851697919</v>
+        <v>2.850946995583345</v>
       </c>
       <c r="K4">
-        <v>3944.571241543943</v>
+        <v>3823.176940017177</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -3469,16 +3933,16 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>188</v>
+      <c r="A1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B1" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B2">
         <v>8700000</v>
@@ -3486,26 +3950,26 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B3">
-        <v>8476754.202064242</v>
+        <v>8479590.132587632</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B4">
-        <v>8247156.249845068</v>
+        <v>8253070.573919045</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B5">
-        <v>8010637.823423402</v>
+        <v>8019907.674655082</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -3513,20 +3977,20 @@
         <v>149</v>
       </c>
       <c r="B6">
-        <v>7735455.61826623</v>
+        <v>7748888.164341453</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="B7">
-        <v>7449576.148832415</v>
+        <v>7467656.390149716</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B8">
         <v>8758481.331682835</v>
@@ -3534,71 +3998,71 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B9">
-        <v>8496918.850601459</v>
+        <v>8500209.805146635</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B10">
-        <v>8226615.089618172</v>
+        <v>8233529.345266046</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="B11">
-        <v>8032054.409684942</v>
+        <v>8041736.906089736</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B12">
-        <v>7832408.175842476</v>
+        <v>7845074.721111168</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="B13">
-        <v>7627263.289575088</v>
+        <v>7643158.537122125</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="B14">
-        <v>7409513.485826758</v>
+        <v>7429029.878354515</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="B15">
-        <v>7184817.987150718</v>
+        <v>7208300.25772877</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B16">
-        <v>6952473.518239986</v>
+        <v>6980325.270833372</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="B17">
         <v>8758481.331682835</v>
@@ -3606,55 +4070,55 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="B18">
-        <v>8571822.2119294</v>
+        <v>8574128.593491327</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="B19">
-        <v>8380796.176403366</v>
+        <v>8385570.050553365</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="B20">
-        <v>8185081.59519545</v>
+        <v>8192505.249674703</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="B21">
-        <v>7984323.078793087</v>
+        <v>7994600.118958353</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="B22">
-        <v>7778110.194919406</v>
+        <v>7791472.955083853</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="B23">
-        <v>7565984.567129556</v>
+        <v>7582697.115993719</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="B24">
         <v>8758481.331682835</v>
@@ -3662,50 +4126,50 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="B25">
-        <v>8572396.711523501</v>
+        <v>8574678.426173495</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="B26">
-        <v>8381972.647276633</v>
+        <v>8386695.332215465</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="B27">
-        <v>8186890.613454849</v>
+        <v>8194234.416009014</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>168</v>
+        <v>190</v>
       </c>
       <c r="B28">
-        <v>7986798.75156553</v>
+        <v>7996964.814865724</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>169</v>
+        <v>192</v>
       </c>
       <c r="B29">
-        <v>7781291.00300254</v>
+        <v>7794508.752074498</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="B30">
-        <v>7569913.88275066</v>
+        <v>7586443.998568771</v>
       </c>
     </row>
   </sheetData>
@@ -3719,37 +4183,37 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>195</v>
+      <c r="A1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C1" t="s">
+        <v>211</v>
+      </c>
+      <c r="D1" t="s">
+        <v>212</v>
+      </c>
+      <c r="E1" t="s">
+        <v>213</v>
+      </c>
+      <c r="F1" t="s">
+        <v>214</v>
+      </c>
+      <c r="G1" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B2">
         <v>19.78565086669546</v>
       </c>
       <c r="C2">
-        <v>19.78565001292267</v>
+        <v>19.78565072830217</v>
       </c>
       <c r="D2">
         <v>58.14923187271204</v>
@@ -3758,21 +4222,21 @@
         <v>1150.5204</v>
       </c>
       <c r="F2">
-        <v>1150.520350353768</v>
+        <v>1150.520391952537</v>
       </c>
       <c r="G2">
-        <v>-4.315110943556593E-06</v>
+        <v>-6.994628940775776E-07</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="B3">
         <v>51.44269156552292</v>
       </c>
       <c r="C3">
-        <v>51.44269156511885</v>
+        <v>51.44269156549727</v>
       </c>
       <c r="D3">
         <v>58.14923187271204</v>
@@ -3781,21 +4245,21 @@
         <v>2991.353</v>
       </c>
       <c r="F3">
-        <v>2991.352999976504</v>
+        <v>2991.352999998508</v>
       </c>
       <c r="G3">
-        <v>-7.854788127821522E-10</v>
+        <v>-4.98624624418578E-11</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>196</v>
+        <v>216</v>
       </c>
       <c r="B4">
         <v>39.57130173339092</v>
       </c>
       <c r="C4">
-        <v>39.57130173308009</v>
+        <v>39.57130173337119</v>
       </c>
       <c r="D4">
         <v>58.14923187271204</v>
@@ -3804,10 +4268,843 @@
         <v>2301.0408</v>
       </c>
       <c r="F4">
-        <v>2301.040799981926</v>
+        <v>2301.040799998853</v>
       </c>
       <c r="G4">
-        <v>-7.854857084369678E-10</v>
+        <v>-4.986384300673128E-11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I50"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B3" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>223</v>
+      </c>
+      <c r="B4" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>225</v>
+      </c>
+      <c r="B5" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>227</v>
+      </c>
+      <c r="B6" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>229</v>
+      </c>
+      <c r="B7" t="s">
+        <v>230</v>
+      </c>
+      <c r="C7" t="s">
+        <v>231</v>
+      </c>
+      <c r="D7" t="s">
+        <v>232</v>
+      </c>
+      <c r="E7" t="s">
+        <v>231</v>
+      </c>
+      <c r="F7" t="s">
+        <v>233</v>
+      </c>
+      <c r="G7" t="s">
+        <v>231</v>
+      </c>
+      <c r="H7" t="s">
+        <v>234</v>
+      </c>
+      <c r="I7" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>235</v>
+      </c>
+      <c r="B8" t="s">
+        <v>236</v>
+      </c>
+      <c r="C8" t="s">
+        <v>237</v>
+      </c>
+      <c r="D8" t="s">
+        <v>238</v>
+      </c>
+      <c r="E8" t="s">
+        <v>239</v>
+      </c>
+      <c r="F8" t="s">
+        <v>240</v>
+      </c>
+      <c r="G8" t="s">
+        <v>241</v>
+      </c>
+      <c r="H8" t="s">
+        <v>242</v>
+      </c>
+      <c r="I8" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>244</v>
+      </c>
+      <c r="B9" t="s">
+        <v>245</v>
+      </c>
+      <c r="C9" t="s">
+        <v>231</v>
+      </c>
+      <c r="D9" t="s">
+        <v>232</v>
+      </c>
+      <c r="E9" t="s">
+        <v>231</v>
+      </c>
+      <c r="F9" t="s">
+        <v>234</v>
+      </c>
+      <c r="G9" t="s">
+        <v>222</v>
+      </c>
+      <c r="H9" t="s">
+        <v>246</v>
+      </c>
+      <c r="I9" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>248</v>
+      </c>
+      <c r="B10" t="s">
+        <v>245</v>
+      </c>
+      <c r="C10" t="s">
+        <v>231</v>
+      </c>
+      <c r="D10" t="s">
+        <v>242</v>
+      </c>
+      <c r="E10" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>249</v>
+      </c>
+      <c r="B11" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" t="s">
+        <v>250</v>
+      </c>
+      <c r="B12" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" t="s">
+        <v>251</v>
+      </c>
+      <c r="B13" t="s">
+        <v>245</v>
+      </c>
+      <c r="C13" t="s">
+        <v>231</v>
+      </c>
+      <c r="D13" t="s">
+        <v>242</v>
+      </c>
+      <c r="E13" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" t="s">
+        <v>252</v>
+      </c>
+      <c r="B14" t="s">
+        <v>245</v>
+      </c>
+      <c r="C14" t="s">
+        <v>231</v>
+      </c>
+      <c r="D14" t="s">
+        <v>253</v>
+      </c>
+      <c r="E14" t="s">
+        <v>231</v>
+      </c>
+      <c r="F14" t="s">
+        <v>242</v>
+      </c>
+      <c r="G14" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" t="s">
+        <v>254</v>
+      </c>
+      <c r="B15" t="s">
+        <v>245</v>
+      </c>
+      <c r="C15" t="s">
+        <v>231</v>
+      </c>
+      <c r="D15" t="s">
+        <v>242</v>
+      </c>
+      <c r="E15" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
+        <v>255</v>
+      </c>
+      <c r="B16" t="s">
+        <v>245</v>
+      </c>
+      <c r="C16" t="s">
+        <v>231</v>
+      </c>
+      <c r="D16" t="s">
+        <v>242</v>
+      </c>
+      <c r="E16" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" t="s">
+        <v>256</v>
+      </c>
+      <c r="B17" t="s">
+        <v>245</v>
+      </c>
+      <c r="C17" t="s">
+        <v>231</v>
+      </c>
+      <c r="D17" t="s">
+        <v>242</v>
+      </c>
+      <c r="E17" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" t="s">
+        <v>257</v>
+      </c>
+      <c r="B18" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" t="s">
+        <v>258</v>
+      </c>
+      <c r="B19" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" t="s">
+        <v>259</v>
+      </c>
+      <c r="B20" t="s">
+        <v>245</v>
+      </c>
+      <c r="C20" t="s">
+        <v>231</v>
+      </c>
+      <c r="D20" t="s">
+        <v>260</v>
+      </c>
+      <c r="E20" t="s">
+        <v>261</v>
+      </c>
+      <c r="F20" t="s">
+        <v>262</v>
+      </c>
+      <c r="G20" t="s">
+        <v>263</v>
+      </c>
+      <c r="H20" t="s">
+        <v>264</v>
+      </c>
+      <c r="I20" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" t="s">
+        <v>265</v>
+      </c>
+      <c r="B21" t="s">
+        <v>245</v>
+      </c>
+      <c r="C21" t="s">
+        <v>231</v>
+      </c>
+      <c r="D21" t="s">
+        <v>260</v>
+      </c>
+      <c r="E21" t="s">
+        <v>266</v>
+      </c>
+      <c r="F21" t="s">
+        <v>262</v>
+      </c>
+      <c r="G21" t="s">
+        <v>263</v>
+      </c>
+      <c r="H21" t="s">
+        <v>264</v>
+      </c>
+      <c r="I21" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" t="s">
+        <v>267</v>
+      </c>
+      <c r="B22" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" t="s">
+        <v>269</v>
+      </c>
+      <c r="B23" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" t="s">
+        <v>271</v>
+      </c>
+      <c r="B24" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" t="s">
+        <v>272</v>
+      </c>
+      <c r="B25" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" t="s">
+        <v>274</v>
+      </c>
+      <c r="B26" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" t="s">
+        <v>275</v>
+      </c>
+      <c r="B27" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" t="s">
+        <v>276</v>
+      </c>
+      <c r="B28" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" t="s">
+        <v>277</v>
+      </c>
+      <c r="B29" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" t="s">
+        <v>279</v>
+      </c>
+      <c r="B30" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" t="s">
+        <v>281</v>
+      </c>
+      <c r="B31" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" t="s">
+        <v>283</v>
+      </c>
+      <c r="B32" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" t="s">
+        <v>285</v>
+      </c>
+      <c r="B33" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" t="s">
+        <v>286</v>
+      </c>
+      <c r="B34" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" t="s">
+        <v>287</v>
+      </c>
+      <c r="B35" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" t="s">
+        <v>289</v>
+      </c>
+      <c r="B36" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" t="s">
+        <v>291</v>
+      </c>
+      <c r="B37" t="s">
+        <v>292</v>
+      </c>
+      <c r="C37" t="s">
+        <v>222</v>
+      </c>
+      <c r="D37" t="s">
+        <v>293</v>
+      </c>
+      <c r="E37" t="s">
+        <v>261</v>
+      </c>
+      <c r="F37" t="s">
+        <v>294</v>
+      </c>
+      <c r="G37" t="s">
+        <v>226</v>
+      </c>
+      <c r="H37" t="s">
+        <v>295</v>
+      </c>
+      <c r="I37" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" t="s">
+        <v>297</v>
+      </c>
+      <c r="B38" t="s">
+        <v>292</v>
+      </c>
+      <c r="C38" t="s">
+        <v>222</v>
+      </c>
+      <c r="D38" t="s">
+        <v>293</v>
+      </c>
+      <c r="E38" t="s">
+        <v>261</v>
+      </c>
+      <c r="F38" t="s">
+        <v>294</v>
+      </c>
+      <c r="G38" t="s">
+        <v>226</v>
+      </c>
+      <c r="H38" t="s">
+        <v>295</v>
+      </c>
+      <c r="I38" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" t="s">
+        <v>298</v>
+      </c>
+      <c r="B39" t="s">
+        <v>292</v>
+      </c>
+      <c r="C39" t="s">
+        <v>299</v>
+      </c>
+      <c r="D39" t="s">
+        <v>293</v>
+      </c>
+      <c r="E39" t="s">
+        <v>261</v>
+      </c>
+      <c r="F39" t="s">
+        <v>294</v>
+      </c>
+      <c r="G39" t="s">
+        <v>226</v>
+      </c>
+      <c r="H39" t="s">
+        <v>295</v>
+      </c>
+      <c r="I39" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" t="s">
+        <v>300</v>
+      </c>
+      <c r="B40" t="s">
+        <v>292</v>
+      </c>
+      <c r="C40" t="s">
+        <v>222</v>
+      </c>
+      <c r="D40" t="s">
+        <v>293</v>
+      </c>
+      <c r="E40" t="s">
+        <v>261</v>
+      </c>
+      <c r="F40" t="s">
+        <v>294</v>
+      </c>
+      <c r="G40" t="s">
+        <v>226</v>
+      </c>
+      <c r="H40" t="s">
+        <v>295</v>
+      </c>
+      <c r="I40" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" t="s">
+        <v>301</v>
+      </c>
+      <c r="B41" t="s">
+        <v>292</v>
+      </c>
+      <c r="C41" t="s">
+        <v>302</v>
+      </c>
+      <c r="D41" t="s">
+        <v>293</v>
+      </c>
+      <c r="E41" t="s">
+        <v>261</v>
+      </c>
+      <c r="F41" t="s">
+        <v>294</v>
+      </c>
+      <c r="G41" t="s">
+        <v>226</v>
+      </c>
+      <c r="H41" t="s">
+        <v>295</v>
+      </c>
+      <c r="I41" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" t="s">
+        <v>303</v>
+      </c>
+      <c r="B42" t="s">
+        <v>292</v>
+      </c>
+      <c r="C42" t="s">
+        <v>304</v>
+      </c>
+      <c r="D42" t="s">
+        <v>293</v>
+      </c>
+      <c r="E42" t="s">
+        <v>261</v>
+      </c>
+      <c r="F42" t="s">
+        <v>294</v>
+      </c>
+      <c r="G42" t="s">
+        <v>226</v>
+      </c>
+      <c r="H42" t="s">
+        <v>295</v>
+      </c>
+      <c r="I42" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" t="s">
+        <v>305</v>
+      </c>
+      <c r="B43" t="s">
+        <v>292</v>
+      </c>
+      <c r="C43" t="s">
+        <v>231</v>
+      </c>
+      <c r="D43" t="s">
+        <v>293</v>
+      </c>
+      <c r="E43" t="s">
+        <v>261</v>
+      </c>
+      <c r="F43" t="s">
+        <v>294</v>
+      </c>
+      <c r="G43" t="s">
+        <v>226</v>
+      </c>
+      <c r="H43" t="s">
+        <v>295</v>
+      </c>
+      <c r="I43" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" t="s">
+        <v>90</v>
+      </c>
+      <c r="B44" t="s">
+        <v>292</v>
+      </c>
+      <c r="C44" t="s">
+        <v>222</v>
+      </c>
+      <c r="D44" t="s">
+        <v>293</v>
+      </c>
+      <c r="E44" t="s">
+        <v>261</v>
+      </c>
+      <c r="F44" t="s">
+        <v>294</v>
+      </c>
+      <c r="G44" t="s">
+        <v>226</v>
+      </c>
+      <c r="H44" t="s">
+        <v>295</v>
+      </c>
+      <c r="I44" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" t="s">
+        <v>306</v>
+      </c>
+      <c r="B45" t="s">
+        <v>292</v>
+      </c>
+      <c r="C45" t="s">
+        <v>222</v>
+      </c>
+      <c r="D45" t="s">
+        <v>293</v>
+      </c>
+      <c r="E45" t="s">
+        <v>261</v>
+      </c>
+      <c r="F45" t="s">
+        <v>294</v>
+      </c>
+      <c r="G45" t="s">
+        <v>226</v>
+      </c>
+      <c r="H45" t="s">
+        <v>295</v>
+      </c>
+      <c r="I45" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" t="s">
+        <v>307</v>
+      </c>
+      <c r="B46" t="s">
+        <v>292</v>
+      </c>
+      <c r="C46" t="s">
+        <v>308</v>
+      </c>
+      <c r="D46" t="s">
+        <v>309</v>
+      </c>
+      <c r="E46" t="s">
+        <v>310</v>
+      </c>
+      <c r="F46" t="s">
+        <v>242</v>
+      </c>
+      <c r="G46" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" t="s">
+        <v>311</v>
+      </c>
+      <c r="B47" t="s">
+        <v>292</v>
+      </c>
+      <c r="C47" t="s">
+        <v>280</v>
+      </c>
+      <c r="D47" t="s">
+        <v>309</v>
+      </c>
+      <c r="E47" t="s">
+        <v>231</v>
+      </c>
+      <c r="F47" t="s">
+        <v>242</v>
+      </c>
+      <c r="G47" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" t="s">
+        <v>312</v>
+      </c>
+      <c r="B48" t="s">
+        <v>292</v>
+      </c>
+      <c r="C48" t="s">
+        <v>280</v>
+      </c>
+      <c r="D48" t="s">
+        <v>309</v>
+      </c>
+      <c r="E48" t="s">
+        <v>231</v>
+      </c>
+      <c r="F48" t="s">
+        <v>242</v>
+      </c>
+      <c r="G48" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" t="s">
+        <v>313</v>
+      </c>
+      <c r="B49" t="s">
+        <v>292</v>
+      </c>
+      <c r="C49" t="s">
+        <v>308</v>
+      </c>
+      <c r="D49" t="s">
+        <v>309</v>
+      </c>
+      <c r="E49" t="s">
+        <v>231</v>
+      </c>
+      <c r="F49" t="s">
+        <v>242</v>
+      </c>
+      <c r="G49" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" t="s">
+        <v>314</v>
+      </c>
+      <c r="B50" t="s">
+        <v>292</v>
+      </c>
+      <c r="C50" t="s">
+        <v>315</v>
+      </c>
+      <c r="D50" t="s">
+        <v>242</v>
+      </c>
+      <c r="E50" t="s">
+        <v>243</v>
       </c>
     </row>
   </sheetData>
